--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7021161</v>
+        <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421832</v>
+        <v>421725</v>
       </c>
       <c r="R2" t="n">
-        <v>6963516</v>
+        <v>6963319</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-10-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-10-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,28 +765,1376 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812373</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136812397</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92290</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>421726</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6963335</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812397</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136813189</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90857</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jättemusseron</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tricholoma colossus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>421825</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6963314</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136813189</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136812498</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91115</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>421746</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6963360</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812498</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136812982</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91115</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>421842</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6963387</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812982</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7021161</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91962</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>421832</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6963516</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-10-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-10-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Hugo Ström</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Hugo Ström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/7021161</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136812608</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93434</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>421771</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6963356</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812608</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136812661</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93403</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>421774</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6963402</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812661</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136813295</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93409</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>421776</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6963288</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136813295</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136812976</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92074</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>421842</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6963387</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812976</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136812538</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>421739</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6963332</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812538</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136812577</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>421748</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6963381</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812577</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136812348</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>421690</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6963342</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812348</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136813052</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>421834</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6963346</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136813052</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136812397</v>
+        <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>92290</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421726</v>
+        <v>421836</v>
       </c>
       <c r="R3" t="n">
-        <v>6963335</v>
+        <v>6963516</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,16 +878,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812397</t>
+          <t>https://artportalen.se/Sighting/136838493</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136813189</v>
+        <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>92290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1596</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421825</v>
+        <v>421726</v>
       </c>
       <c r="R4" t="n">
-        <v>6963314</v>
+        <v>6963335</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -980,38 +980,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136813189</t>
+          <t>https://artportalen.se/Sighting/136812397</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136812498</v>
+        <v>136813189</v>
       </c>
       <c r="B5" t="n">
-        <v>91115</v>
+        <v>90857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>1596</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421746</v>
+        <v>421825</v>
       </c>
       <c r="R5" t="n">
-        <v>6963360</v>
+        <v>6963314</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1082,13 +1082,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812498</t>
+          <t>https://artportalen.se/Sighting/136813189</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136812982</v>
+        <v>136812498</v>
       </c>
       <c r="B6" t="n">
         <v>91115</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421842</v>
+        <v>421746</v>
       </c>
       <c r="R6" t="n">
-        <v>6963387</v>
+        <v>6963360</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812982</t>
+          <t>https://artportalen.se/Sighting/136812498</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7021161</v>
+        <v>136812982</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>91115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421832</v>
+        <v>421842</v>
       </c>
       <c r="R7" t="n">
-        <v>6963516</v>
+        <v>6963387</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-10-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-10-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,31 +1275,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7021161</t>
+          <t>https://artportalen.se/Sighting/136812982</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136812608</v>
+        <v>7021161</v>
       </c>
       <c r="B8" t="n">
-        <v>93434</v>
+        <v>91962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,37 +1303,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3100</v>
+        <v>2079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+          <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421771</v>
+        <v>421832</v>
       </c>
       <c r="R8" t="n">
-        <v>6963356</v>
+        <v>6963516</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1361,12 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2013-10-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2013-10-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,27 +1377,31 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812608</t>
+          <t>https://artportalen.se/Sighting/7021161</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136812661</v>
+        <v>136812608</v>
       </c>
       <c r="B9" t="n">
-        <v>93403</v>
+        <v>93434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421774</v>
+        <v>421771</v>
       </c>
       <c r="R9" t="n">
-        <v>6963402</v>
+        <v>6963356</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,16 +1494,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812661</t>
+          <t>https://artportalen.se/Sighting/136812608</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136813295</v>
+        <v>136812661</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421776</v>
+        <v>421774</v>
       </c>
       <c r="R10" t="n">
-        <v>6963288</v>
+        <v>6963402</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1596,38 +1596,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136813295</t>
+          <t>https://artportalen.se/Sighting/136812661</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136812976</v>
+        <v>136813295</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>93409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421842</v>
+        <v>421776</v>
       </c>
       <c r="R11" t="n">
-        <v>6963387</v>
+        <v>6963288</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1698,38 +1698,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812976</t>
+          <t>https://artportalen.se/Sighting/136813295</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136812538</v>
+        <v>136839197</v>
       </c>
       <c r="B12" t="n">
-        <v>78879</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421739</v>
+        <v>421699</v>
       </c>
       <c r="R12" t="n">
-        <v>6963332</v>
+        <v>6963530</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,38 +1800,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812538</t>
+          <t>https://artportalen.se/Sighting/136839197</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136812577</v>
+        <v>136812976</v>
       </c>
       <c r="B13" t="n">
-        <v>80095</v>
+        <v>92074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421748</v>
+        <v>421842</v>
       </c>
       <c r="R13" t="n">
-        <v>6963381</v>
+        <v>6963387</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1902,16 +1902,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812577</t>
+          <t>https://artportalen.se/Sighting/136812976</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136812348</v>
+        <v>136812538</v>
       </c>
       <c r="B14" t="n">
-        <v>58169</v>
+        <v>78879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,43 +1919,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421690</v>
+        <v>421739</v>
       </c>
       <c r="R14" t="n">
-        <v>6963342</v>
+        <v>6963332</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2013,38 +2004,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812348</t>
+          <t>https://artportalen.se/Sighting/136812538</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136813052</v>
+        <v>136812577</v>
       </c>
       <c r="B15" t="n">
-        <v>98219</v>
+        <v>80095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2054,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421834</v>
+        <v>421748</v>
       </c>
       <c r="R15" t="n">
-        <v>6963346</v>
+        <v>6963381</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2115,7 +2106,322 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136812577</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136812348</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>421690</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6963342</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136812348</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136813052</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>421834</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6963346</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136813052</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136839098</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93405</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>421758</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6963582</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136839098</t>
         </is>
       </c>
     </row>
@@ -2135,6 +2441,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136813189</v>
       </c>
       <c r="B5" t="n">
-        <v>90857</v>
+        <v>90859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812498</v>
       </c>
       <c r="B6" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136812982</v>
       </c>
       <c r="B7" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812608</v>
       </c>
       <c r="B9" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136812661</v>
       </c>
       <c r="B10" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136813295</v>
       </c>
       <c r="B11" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812976</v>
       </c>
       <c r="B13" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>136813052</v>
       </c>
       <c r="B17" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136813189</v>
+        <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>90859</v>
+        <v>91117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1596</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421825</v>
+        <v>421746</v>
       </c>
       <c r="R5" t="n">
-        <v>6963314</v>
+        <v>6963360</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1082,13 +1082,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136813189</t>
+          <t>https://artportalen.se/Sighting/136812498</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136812498</v>
+        <v>136812982</v>
       </c>
       <c r="B6" t="n">
         <v>91117</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421746</v>
+        <v>421842</v>
       </c>
       <c r="R6" t="n">
-        <v>6963360</v>
+        <v>6963387</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1184,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812498</t>
+          <t>https://artportalen.se/Sighting/136812982</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136812982</v>
+        <v>7021161</v>
       </c>
       <c r="B7" t="n">
-        <v>91117</v>
+        <v>91962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1201,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+          <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421842</v>
+        <v>421832</v>
       </c>
       <c r="R7" t="n">
-        <v>6963387</v>
+        <v>6963516</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2013-10-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2013-10-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,27 +1275,31 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812982</t>
+          <t>https://artportalen.se/Sighting/7021161</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7021161</v>
+        <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>91962</v>
+        <v>93436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,37 +1307,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421832</v>
+        <v>421771</v>
       </c>
       <c r="R8" t="n">
-        <v>6963516</v>
+        <v>6963356</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-10-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-10-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1377,31 +1381,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7021161</t>
+          <t>https://artportalen.se/Sighting/136812608</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136812608</v>
+        <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93436</v>
+        <v>93405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1409,21 +1409,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421771</v>
+        <v>421774</v>
       </c>
       <c r="R9" t="n">
-        <v>6963356</v>
+        <v>6963402</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1494,16 +1494,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812608</t>
+          <t>https://artportalen.se/Sighting/136812661</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136812661</v>
+        <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93405</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1511,21 +1511,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421774</v>
+        <v>421776</v>
       </c>
       <c r="R10" t="n">
-        <v>6963402</v>
+        <v>6963288</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1596,38 +1596,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812661</t>
+          <t>https://artportalen.se/Sighting/136813295</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136813295</v>
+        <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421776</v>
+        <v>421699</v>
       </c>
       <c r="R11" t="n">
-        <v>6963288</v>
+        <v>6963530</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1698,38 +1698,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136813295</t>
+          <t>https://artportalen.se/Sighting/136839197</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136839197</v>
+        <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>92076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4365</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421699</v>
+        <v>421842</v>
       </c>
       <c r="R12" t="n">
-        <v>6963530</v>
+        <v>6963387</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,38 +1800,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136839197</t>
+          <t>https://artportalen.se/Sighting/136812976</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136812976</v>
+        <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>92076</v>
+        <v>78879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421842</v>
+        <v>421739</v>
       </c>
       <c r="R13" t="n">
-        <v>6963387</v>
+        <v>6963332</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1902,13 +1902,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812976</t>
+          <t>https://artportalen.se/Sighting/136812538</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136812538</v>
+        <v>136917945</v>
       </c>
       <c r="B14" t="n">
         <v>78879</v>
@@ -1939,17 +1939,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+          <t>Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>421739</v>
+        <v>421832</v>
       </c>
       <c r="R14" t="n">
-        <v>6963332</v>
+        <v>6963521</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,16 +2004,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812538</t>
+          <t>https://artportalen.se/Sighting/136917945</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136812577</v>
+        <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>80095</v>
+        <v>78879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,37 +2021,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+          <t>Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>421748</v>
+        <v>421737</v>
       </c>
       <c r="R15" t="n">
-        <v>6963381</v>
+        <v>6963342</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,16 +2106,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812577</t>
+          <t>https://artportalen.se/Sighting/136917949</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136812348</v>
+        <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>80095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2123,43 +2123,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421690</v>
+        <v>421748</v>
       </c>
       <c r="R16" t="n">
-        <v>6963342</v>
+        <v>6963381</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2217,51 +2208,60 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136812348</t>
+          <t>https://artportalen.se/Sighting/136812577</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136813052</v>
+        <v>136812348</v>
       </c>
       <c r="B17" t="n">
-        <v>98221</v>
+        <v>58169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421834</v>
+        <v>421690</v>
       </c>
       <c r="R17" t="n">
-        <v>6963346</v>
+        <v>6963342</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2319,38 +2319,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136813052</t>
+          <t>https://artportalen.se/Sighting/136812348</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136839098</v>
+        <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>93405</v>
+        <v>98221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421758</v>
+        <v>421834</v>
       </c>
       <c r="R18" t="n">
-        <v>6963582</v>
+        <v>6963346</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2421,7 +2421,507 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136813052</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136917946</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>421832</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6963521</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136917946</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136917951</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>421737</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6963343</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136917951</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136917948</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80370</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>421833</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6963521</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136917948</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136839098</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93405</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>421758</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6963582</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136839098</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136917943</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80370</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ringbrynnsbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>421768</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6963581</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136917943</t>
         </is>
       </c>
     </row>
@@ -2444,6 +2944,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92359</v>
+        <v>92361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80370</v>
+        <v>80374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80370</v>
+        <v>80374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92361</v>
+        <v>92363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80374</v>
+        <v>80376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80374</v>
+        <v>80376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92363</v>
+        <v>92364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80376</v>
+        <v>80377</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80376</v>
+        <v>80377</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92364</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92303</v>
+        <v>92307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80377</v>
+        <v>80379</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80377</v>
+        <v>80379</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -2328,7 +2328,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92374</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92307</v>
+        <v>92309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80379</v>
+        <v>80382</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80379</v>
+        <v>80382</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92309</v>
+        <v>92322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>136812348</v>
       </c>
       <c r="B17" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80382</v>
+        <v>80395</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80382</v>
+        <v>80395</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92322</v>
+        <v>92324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>136812348</v>
       </c>
       <c r="B17" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80395</v>
+        <v>80397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80395</v>
+        <v>80397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -2247,11 +2247,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ringbrynnsbäcken, Ringbrynnsbäcken, Hjd</t>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92391</v>
+        <v>92394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92324</v>
+        <v>92327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92394</v>
+        <v>92404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92327</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>136812348</v>
       </c>
       <c r="B17" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80397</v>
+        <v>80407</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80397</v>
+        <v>80407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92404</v>
+        <v>92405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92405</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93481</v>
+        <v>93486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>136812348</v>
       </c>
       <c r="B17" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80407</v>
+        <v>80410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92341</v>
+        <v>92343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93486</v>
+        <v>93488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136812373</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136812397</v>
       </c>
       <c r="B4" t="n">
-        <v>92343</v>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136812498</v>
       </c>
       <c r="B5" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136812982</v>
       </c>
       <c r="B6" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136812608</v>
       </c>
       <c r="B8" t="n">
-        <v>93488</v>
+        <v>93494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136812661</v>
       </c>
       <c r="B9" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>136813295</v>
       </c>
       <c r="B10" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>136812976</v>
       </c>
       <c r="B12" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136812538</v>
       </c>
       <c r="B13" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>136812577</v>
       </c>
       <c r="B16" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>136812348</v>
       </c>
       <c r="B17" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>136813052</v>
       </c>
       <c r="B18" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80410</v>
+        <v>80415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136838493</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>136839197</v>
       </c>
       <c r="B11" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80415</v>
+        <v>80426</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>136839098</v>
       </c>
       <c r="B22" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80415</v>
+        <v>80426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80426</v>
+        <v>80427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80426</v>
+        <v>80427</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 27348-2026 artfynd.xlsx
+++ b/artfynd/A 27348-2026 artfynd.xlsx
@@ -1911,7 +1911,7 @@
         <v>136917945</v>
       </c>
       <c r="B14" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         <v>136917949</v>
       </c>
       <c r="B15" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         <v>136917946</v>
       </c>
       <c r="B19" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>136917951</v>
       </c>
       <c r="B20" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>136917948</v>
       </c>
       <c r="B21" t="n">
-        <v>80427</v>
+        <v>80429</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>136917943</v>
       </c>
       <c r="B23" t="n">
-        <v>80427</v>
+        <v>80429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
